--- a/docs/matriz_DEFINITIVA.xlsx
+++ b/docs/matriz_DEFINITIVA.xlsx
@@ -838,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="60" customHeight="1" s="48">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -1650,6 +1651,7 @@
     <row r="2" ht="32.1" customHeight="1" s="48">
       <c r="A2" s="60" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="69.90000000000001" customHeight="1" s="48">
       <c r="A4" s="38" t="inlineStr">
         <is>
@@ -2621,6 +2623,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="90" customHeight="1" s="48">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -3404,7 +3407,11 @@
       <c r="F25" s="30" t="n"/>
       <c r="G25" s="30" t="n"/>
       <c r="H25" s="30" t="n"/>
-      <c r="I25" s="30" t="n"/>
+      <c r="I25" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J25" s="30" t="n"/>
       <c r="K25" s="30" t="n"/>
       <c r="L25" s="30" t="n"/>
@@ -3490,7 +3497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Contratista/ superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -3500,7 +3507,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>El superintendente no se separa; va dentro del contratista, como pidió el profesor.</t>
+          <t>El superintendente actúa como representante operativo del contratista, por lo que se integra como un solo stakeholder y no se separa.</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4324,7 @@
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>El programa nace del 21 fr. VIII y IX LOPSRM (calendarización física y financiera, fechas de inicio y terminación). El 46 fr. V LOPSRM lo incorpora como parte del contrato. Eliminar 131 RLOPSRM (mal usado).</t>
+          <t>El programa nace del 21 fr. VIII y IX LOPSRM (calendarización física y financiera, fechas de inicio y terminación). El 46 fr. V LOPSRM lo incorpora como parte del contrato. Se descarta el 131 RLOPSRM como apoyo (mal usado, no aplica).</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4540,7 @@
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>El 64 LOPSRM regula la recepción y la elaboración del finiquito; el 66 LOPSRM regula la extinción de derechos y obligaciones. Eliminar 124 RLOPSRM porque pertenece a bitácora, no al cierre contractual.</t>
+          <t>El 64 LOPSRM regula la recepción y la elaboración del finiquito; el 66 LOPSRM regula la extinción de derechos y obligaciones. Se descarta el 124 RLOPSRM como apoyo porque pertenece a bitácora, no al cierre contractual.</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4557,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -4622,7 +4629,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -4694,7 +4701,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -4766,7 +4773,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -4838,7 +4845,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -4910,7 +4917,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -4982,7 +4989,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -5054,7 +5061,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -5126,7 +5133,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -5198,7 +5205,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -5270,7 +5277,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -5342,7 +5349,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -5414,7 +5421,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -5685,7 +5692,7 @@
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>La supervisión interviene en bitácora conforme al 122-123 RLOPSRM. Eliminar referencia genérica a 119-124.</t>
+          <t>La supervisión interviene en bitácora conforme al 122-123 RLOPSRM. Se descarta la referencia genérica a 119-124 como apoyo (no aplica).</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5980,7 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>El 53 LOPSRM regula los plazos de ejecución; el 116 RLOPSRM atribuye a la supervisión el seguimiento a variaciones del programa. Eliminar 131 RLOPSRM (mal usado).</t>
+          <t>El 53 LOPSRM regula los plazos de ejecución; el 116 RLOPSRM atribuye a la supervisión el seguimiento a variaciones del programa. Se descarta el 131 RLOPSRM como apoyo (mal usado, no aplica).</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6772,7 @@
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>El 48 LOPSRM regula la constitución de fianzas (anticipo y cumplimiento, dentro de 15 días desde fallo). El 66 LOPSRM regula el régimen de fianzas en finiquito. Eliminar 60 y 61 (rescisión/terminación, otra figura).</t>
+          <t>El 48 LOPSRM regula la constitución de fianzas (anticipo y cumplimiento, dentro de 15 días desde fallo). El 66 LOPSRM regula el régimen de fianzas en finiquito. Se descartan los arts. 60 y 61 LOPSRM como apoyo (rescisión/terminación, otra figura).</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6844,7 @@
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>El 64 LOPSRM regula recepción y elaboración del finiquito; el 66 LOPSRM regula la extinción de derechos y obligaciones. Eliminar 124 RLOPSRM.</t>
+          <t>El 64 LOPSRM regula recepción y elaboración del finiquito; el 66 LOPSRM regula la extinción de derechos y obligaciones. Se descarta el 124 RLOPSRM como apoyo (no aplica).</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7941,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -8006,7 +8013,7 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -8078,7 +8085,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -8150,7 +8157,7 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -8222,7 +8229,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Contratista / superintendente</t>
+          <t>Contratista/Superintendente</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -8277,7 +8284,7 @@
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>Los cambios al programa que generan modificatorios se rigen por 59 LOPSRM. El historial como funcionalidad es operativa. Eliminar 136 RLOPSRM.</t>
+          <t>Los cambios al programa que generan modificatorios se rigen por 59 LOPSRM. El historial como funcionalidad es operativa. Se descarta el 136 RLOPSRM como apoyo (no aplica).</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8428,7 @@
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>El 116 RLOPSRM contempla la memoria fotográfica como obligación de la supervisión. Eliminar 131 RLOPSRM.</t>
+          <t>El 116 RLOPSRM contempla la memoria fotográfica como obligación de la supervisión. Se descarta el 131 RLOPSRM como apoyo (no aplica).</t>
         </is>
       </c>
     </row>
@@ -9217,6 +9224,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="64" t="inlineStr">
         <is>
@@ -9275,6 +9283,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -9450,6 +9459,7 @@
     <row r="2" ht="49.5" customHeight="1" s="48">
       <c r="A2" s="54" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="48">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9921,7 +9931,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>48 LOPSRM (constitución) + 66 LOPSRM (liberación). Eliminar 60 y 61.</t>
+          <t>48 LOPSRM (constitución) + 66 LOPSRM (liberación). Se descartan los arts. 60 y 61 LOPSRM como apoyo (corresponden a rescisión/terminación, otra figura).</t>
         </is>
       </c>
     </row>
@@ -9985,6 +9995,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42" ht="15" customHeight="1" s="48">
       <c r="A42" s="3" t="inlineStr">
         <is>
@@ -10073,6 +10084,8 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52" ht="15" customHeight="1" s="48">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -10115,6 +10128,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="27.9" customHeight="1" s="48">
       <c r="A3" s="12" t="inlineStr">
         <is>

--- a/docs/matriz_DEFINITIVA.xlsx
+++ b/docs/matriz_DEFINITIVA.xlsx
@@ -378,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -556,6 +556,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -841,6 +844,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="60" customHeight="1" s="48">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -1014,7 +1018,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E8" s="30" t="n"/>
+      <c r="E8" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2601,7 +2609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="48" min="1" max="1"/>
@@ -2615,6 +2623,7 @@
     <col width="15" customWidth="1" style="48" min="21" max="21"/>
     <col width="15" customWidth="1" style="48" min="22" max="22"/>
     <col width="15" customWidth="1" style="48" min="23" max="23"/>
+    <col width="15" customWidth="1" style="48" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="48">
@@ -2745,6 +2754,11 @@
       <c r="W4" s="61" t="inlineStr">
         <is>
           <t>Art. 130 RLOPSRM</t>
+        </is>
+      </c>
+      <c r="X4" s="61" t="inlineStr">
+        <is>
+          <t>Art. 117 RLOPSRM</t>
         </is>
       </c>
     </row>
@@ -2788,6 +2802,7 @@
       <c r="U5" s="62" t="n"/>
       <c r="V5" s="62" t="n"/>
       <c r="W5" s="62" t="n"/>
+      <c r="X5" s="62" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2829,6 +2844,7 @@
       <c r="U6" s="62" t="n"/>
       <c r="V6" s="62" t="n"/>
       <c r="W6" s="62" t="n"/>
+      <c r="X6" s="62" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2874,6 +2890,7 @@
       </c>
       <c r="V7" s="62" t="n"/>
       <c r="W7" s="62" t="n"/>
+      <c r="X7" s="62" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -2915,6 +2932,11 @@
       <c r="U8" s="62" t="n"/>
       <c r="V8" s="62" t="n"/>
       <c r="W8" s="62" t="n"/>
+      <c r="X8" s="70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -2952,6 +2974,7 @@
       <c r="U9" s="62" t="n"/>
       <c r="V9" s="62" t="n"/>
       <c r="W9" s="62" t="n"/>
+      <c r="X9" s="62" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -2989,6 +3012,7 @@
       <c r="U10" s="62" t="n"/>
       <c r="V10" s="62" t="n"/>
       <c r="W10" s="62" t="n"/>
+      <c r="X10" s="62" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3026,6 +3050,7 @@
       <c r="U11" s="62" t="n"/>
       <c r="V11" s="62" t="n"/>
       <c r="W11" s="62" t="n"/>
+      <c r="X11" s="62" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3075,6 +3100,7 @@
       <c r="U12" s="62" t="n"/>
       <c r="V12" s="62" t="n"/>
       <c r="W12" s="62" t="n"/>
+      <c r="X12" s="62" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
@@ -3120,6 +3146,7 @@
       <c r="U13" s="62" t="n"/>
       <c r="V13" s="62" t="n"/>
       <c r="W13" s="62" t="n"/>
+      <c r="X13" s="62" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
@@ -3157,6 +3184,7 @@
       <c r="U14" s="62" t="n"/>
       <c r="V14" s="62" t="n"/>
       <c r="W14" s="62" t="n"/>
+      <c r="X14" s="62" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
@@ -3194,6 +3222,7 @@
       <c r="U15" s="62" t="n"/>
       <c r="V15" s="62" t="n"/>
       <c r="W15" s="62" t="n"/>
+      <c r="X15" s="62" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
@@ -3259,6 +3288,7 @@
       <c r="U16" s="62" t="n"/>
       <c r="V16" s="62" t="n"/>
       <c r="W16" s="62" t="n"/>
+      <c r="X16" s="62" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
@@ -3300,6 +3330,7 @@
       <c r="U17" s="62" t="n"/>
       <c r="V17" s="62" t="n"/>
       <c r="W17" s="62" t="n"/>
+      <c r="X17" s="62" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
@@ -3341,6 +3372,7 @@
           <t>X</t>
         </is>
       </c>
+      <c r="X18" s="62" t="n"/>
     </row>
     <row r="19" ht="25.5" customHeight="1" s="48">
       <c r="A19" s="29" t="inlineStr">
@@ -3398,6 +3430,7 @@
       <c r="U19" s="62" t="n"/>
       <c r="V19" s="62" t="n"/>
       <c r="W19" s="62" t="n"/>
+      <c r="X19" s="62" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
@@ -3435,6 +3468,7 @@
       <c r="U20" s="62" t="n"/>
       <c r="V20" s="62" t="n"/>
       <c r="W20" s="62" t="n"/>
+      <c r="X20" s="62" t="n"/>
     </row>
     <row r="21" ht="25.5" customHeight="1" s="48">
       <c r="A21" s="29" t="inlineStr">
@@ -3472,6 +3506,7 @@
       <c r="U21" s="62" t="n"/>
       <c r="V21" s="62" t="n"/>
       <c r="W21" s="62" t="n"/>
+      <c r="X21" s="62" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
@@ -3509,6 +3544,7 @@
       <c r="U22" s="62" t="n"/>
       <c r="V22" s="62" t="n"/>
       <c r="W22" s="62" t="n"/>
+      <c r="X22" s="62" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
@@ -3546,6 +3582,7 @@
       <c r="U23" s="62" t="n"/>
       <c r="V23" s="62" t="n"/>
       <c r="W23" s="62" t="n"/>
+      <c r="X23" s="62" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
@@ -3595,6 +3632,7 @@
         </is>
       </c>
       <c r="W24" s="62" t="n"/>
+      <c r="X24" s="62" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
@@ -3636,6 +3674,7 @@
       <c r="U25" s="62" t="n"/>
       <c r="V25" s="62" t="n"/>
       <c r="W25" s="62" t="n"/>
+      <c r="X25" s="62" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9660,7 +9699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="30" customWidth="1" style="48" min="1" max="1"/>
@@ -9674,6 +9713,7 @@
     <row r="2" ht="49.5" customHeight="1" s="48">
       <c r="A2" s="54" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="48">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10109,291 +10149,304 @@
     <row r="30" ht="30" customHeight="1" s="48">
       <c r="A30" s="66" t="inlineStr">
         <is>
+          <t>117 RLOPSRM</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>Obligación del superintendente de conocer el contrato</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>El superintendente (integrado en el rol Contratista) debe conocer con amplitud el catálogo de conceptos, programas de ejecución, planos, bitácora, convenios y demás documentos del contrato. Fundamenta el acceso de consulta del contratista al expediente (HU-04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" s="48">
+      <c r="A31" s="66" t="inlineStr">
+        <is>
           <t>191 LFD</t>
         </is>
       </c>
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B31" s="67" t="inlineStr">
         <is>
           <t>Retención del 5 al millar sobre estimaciones (Ley Federal de Derechos)</t>
         </is>
       </c>
-      <c r="C30" s="67" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1" s="48">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="C31" s="67" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1" s="48">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Reglas globales aplicadas</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="48">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33" ht="30" customHeight="1" s="48">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Regla aplicada</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1" s="48">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Bitácora</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Anclaje a Ley en 46 último párrafo LOPSRM. Régimen reglamentario en 122-123 RLOPSRM. Notas por rol en 125 RLOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="48">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Estimaciones</t>
+          <t>Bitácora</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Base 54 LOPSRM (6/15/20 días). Apoyo correcto: 132 RLOPSRM. Afirmativa ficta: 133 RLOPSRM.</t>
+          <t>Anclaje a Ley en 46 último párrafo LOPSRM. Régimen reglamentario en 122-123 RLOPSRM. Notas por rol en 125 RLOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="48">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Pagos en mora</t>
+          <t>Estimaciones</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>55 LOPSRM (gastos financieros con tasa de recargos por mora fiscal).</t>
+          <t>Base 54 LOPSRM (6/15/20 días). Apoyo correcto: 132 RLOPSRM. Afirmativa ficta: 133 RLOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="48">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Anticipos</t>
+          <t>Pagos en mora</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>50 LOPSRM (otorgamiento, amortización, atraso). Garantía de anticipo: 48 fr. I LOPSRM.</t>
+          <t>55 LOPSRM (gastos financieros con tasa de recargos por mora fiscal).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="48">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Modificatorios</t>
+          <t>Anticipos</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>59 LOPSRM exclusivamente. El 136 RLOPSRM (ajuste de costos) NO aplica como apoyo general.</t>
+          <t>50 LOPSRM (otorgamiento, amortización, atraso). Garantía de anticipo: 48 fr. I LOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="48">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Programa de obra</t>
+          <t>Modificatorios</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>21 fr. VIII-IX LOPSRM (calendarización) + 46 fr. V LOPSRM (parte del contrato).</t>
+          <t>59 LOPSRM exclusivamente. El 136 RLOPSRM (ajuste de costos) NO aplica como apoyo general.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1" s="48">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Supervisión</t>
+          <t>Programa de obra</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>53 segundo párrafo LOPSRM + 113-116 RLOPSRM.</t>
+          <t>21 fr. VIII-IX LOPSRM (calendarización) + 46 fr. V LOPSRM (parte del contrato).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" s="48">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Fianzas</t>
+          <t>Supervisión</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>48 LOPSRM (constitución) + 66 LOPSRM (liberación). Se descartan los arts. 60 y 61 LOPSRM como apoyo (corresponden a rescisión/terminación, otra figura).</t>
+          <t>53 segundo párrafo LOPSRM + 113-116 RLOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Cierre y finiquito</t>
+          <t>Fianzas</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>64 y 66 LOPSRM. NO usar 124 RLOPSRM.</t>
+          <t>48 LOPSRM (constitución) + 66 LOPSRM (liberación). Se descartan los arts. 60 y 61 LOPSRM como apoyo (corresponden a rescisión/terminación, otra figura).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="48">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Penas convencionales</t>
+          <t>Cierre y finiquito</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>46 Bis LOPSRM. Deductivas asociadas al 46 fr. X LOPSRM.</t>
+          <t>64 y 66 LOPSRM. NO usar 124 RLOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Suficiencia presupuestal</t>
+          <t>Penas convencionales</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24 LOPSRM (remite a LFPRH).</t>
+          <t>46 Bis LOPSRM. Deductivas asociadas al 46 fr. X LOPSRM.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="27.75" customHeight="1" s="48">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Visualizaciones del sistema</t>
+          <t>Suficiencia presupuestal</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Tableros, dashboards, exportaciones, búsquedas, alertas, semáforos: Operativo o Sin fundamento expreso.</t>
+          <t>24 LOPSRM (remite a LFPRH).</t>
         </is>
       </c>
     </row>
     <row r="45" ht="27.75" customHeight="1" s="48">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>Visualizaciones del sistema</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Tableros, dashboards, exportaciones, búsquedas, alertas, semáforos: Operativo o Sin fundamento expreso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="27.75" customHeight="1" s="48">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>Materia fiscal</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>CFDI (CFF, RMF SAT), retenciones (LFD, ISR, IVA), cartera vencida: fuera de LOPSRM, son operativos.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="27.75" customHeight="1" s="48"/>
-    <row r="47" ht="27.75" customHeight="1" s="48">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="47" ht="27.75" customHeight="1" s="48"/>
+    <row r="48" ht="27.75" customHeight="1" s="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Fuentes oficiales consultadas</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="27.75" customHeight="1" s="48">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="49" ht="27.75" customHeight="1" s="48">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>URL / referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="27.75" customHeight="1" s="48">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>LOPSRM (texto vigente)</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Cámara de Diputados, Última Reforma DOF 14-11-2025: https://www.diputados.gob.mx/LeyesBiblio/pdf/LOPSRM.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>RLOPSRM (Reglamento)</t>
+          <t>LOPSRM (texto vigente)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cámara de Diputados: https://www.diputados.gob.mx/LeyesBiblio/regley/Reg_LOPSRM.pdf</t>
+          <t>Cámara de Diputados, Última Reforma DOF 14-11-2025: https://www.diputados.gob.mx/LeyesBiblio/pdf/LOPSRM.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Reforma LOPSRM 2025</t>
+          <t>RLOPSRM (Reglamento)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>DOF 16-04-2025 (modernización; flexibilización art. 59)</t>
+          <t>Cámara de Diputados: https://www.diputados.gob.mx/LeyesBiblio/regley/Reg_LOPSRM.pdf</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="48">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>Reforma LOPSRM 2025</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>DOF 16-04-2025 (modernización; flexibilización art. 59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="139.5" customHeight="1" s="48">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>Reforma LOPSRM 14-11-2025</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>DOF 14-11-2025 (última reforma vigente)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="139.5" customHeight="1" s="48">
-      <c r="A53" s="66" t="n"/>
-      <c r="B53" s="67" t="n"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Las dependencias y entidades que realicen obras públicas están obligadas a retener un cinco al millar sobre el importe de cada estimación de trabajo, destinado a la Secretaría de la Función Pública para servicios de inspección, control y vigilancia. Es el fundamento legal de la retención del 5 al millar mencionada en SRV-04-01 y SRV-05-01.</t>
-        </is>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="66" t="n"/>
+      <c r="B54" s="58" t="n"/>
+      <c r="C54" s="59" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Manuales operativos del Art. 54</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SCT, despachos especializados (cobro de estimaciones)</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56"/>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Declaración del responsable de la depuración</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="54" t="n"/>
+    <row r="59">
+      <c r="A59" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/matriz_DEFINITIVA.xlsx
+++ b/docs/matriz_DEFINITIVA.xlsx
@@ -844,7 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="60" customHeight="1" s="48">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -9713,7 +9712,6 @@
     <row r="2" ht="49.5" customHeight="1" s="48">
       <c r="A2" s="54" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="48">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10408,16 +10406,13 @@
       </c>
     </row>
     <row r="53" ht="139.5" customHeight="1" s="48">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="66" t="inlineStr">
         <is>
           <t>Reforma LOPSRM 14-11-2025</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>DOF 14-11-2025 (última reforma vigente)</t>
-        </is>
-      </c>
+      <c r="B53" s="58" t="n"/>
+      <c r="C53" s="59" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="66" t="n"/>
@@ -10436,8 +10431,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11402,7 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>1) Apertura del periodo conforme al plazo del contrato y al art. 132 RLOPSRM (estructura de la carátula).
+          <t>1) Apertura del periodo conforme al plazo del contrato y al art. 132 RLOPSRM (documentos soporte que acompañan la estimación).
 2) Cálculos administrativos en la carátula: anticipo y su amortización (art. 50 LOPSRM), retenciones legales (5 al millar conforme al art. 191 LFD) y deductivas por penalizaciones (art. 46 Bis LOPSRM).</t>
         </is>
       </c>
@@ -11605,7 +11598,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>1) Plazo de revisión: 15 días naturales (supervisión) + 5 días para autorización por residencia, dentro de los 20 días del art. 54 LOPSRM.
+          <t>1) Plazo de revisión y autorización: hasta 15 días naturales tras la presentación de la estimación (art. 54 LOPSRM). El pago corre por separado (ver SRV-07-01).
 2) Afirmativa ficta del art. 133 RLOPSRM: si no se emiten observaciones en el plazo, se considera que no las hay.
 3) Anticipos y amortización conforme art. 50 LOPSRM; retenciones y deductivas según contrato.</t>
         </is>

--- a/docs/matriz_DEFINITIVA.xlsx
+++ b/docs/matriz_DEFINITIVA.xlsx
@@ -10719,20 +10719,25 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>• Captura los datos generales del contrato y el PDF firmado.
-• Carga el catálogo de conceptos completo con clave, descripción, unidad, precio y cantidad.
-• Registra el programa de obra mes a mes por concepto.
-• Guarda los elementos jurídicos del contratista.
-• Versiona la configuración inicial para que después pueda actualizarse por modificatorios.</t>
+          <t>• Captura los datos generales del contrato (folio único, partes, monto, plazos, modalidad de pago).
+• Carga el catálogo de conceptos completo (clave, descripción, unidad, precio unitario, cantidad contratada).
+• Registra el programa de obra (calendario de ejecución por concepto, mes a mes).
+• Registra los elementos jurídicos, separando los de la dependencia (representante, facultades, fundamento de contratación) de los del contratista (representante legal, datos fiscales, poder).
+• Registra las garantías: póliza de anticipo, póliza de cumplimiento y garantía de vicios ocultos según lo pactado (cláusula y/o póliza) — fundamento art. 48 LOPSRM.
+• Registra el plan de amortización del anticipo y las penalizaciones aplicables, incluida la retención del 5 al millar sobre estimaciones (art. 191 LFD).
+• Guarda el PDF firmado del contrato como respaldo documental.
+• Valida que los campos obligatorios estén completos y el folio sea único antes de guardar.
+• Versiona la configuración inicial para que pueda actualizarse por modificatorios (SRV-01-03).</t>
         </is>
       </c>
       <c r="F2" s="14" t="inlineStr">
         <is>
-          <t>• No genera el contrato (asume que ya está firmado fuera del sistema).
-• No edita el PDF del contrato firmado (es inmutable).
-• No valida si el contrato cumple legalmente (eso ya lo hizo la dependencia antes de firmarlo).
-• No interactúa con CompraNet, SAT ni sistemas externos.
-• No autoriza ni rechaza el contrato (solo lo captura).</t>
+          <t>• No genera el contrato (ya está firmado fuera del sistema antes de capturarse).
+• No edita el PDF firmado (es inmutable; cualquier cambio requiere modificatorio).
+• No valida la legalidad del contrato (lo hizo la dependencia antes de firmar).
+• No interactúa con CompraNet, SAT ni afianzadoras.
+• No autoriza ni rechaza el contrato (solo captura).
+• No registra estimaciones ni pagos (SRV-04-* / SRV-07-*).</t>
         </is>
       </c>
       <c r="G2" s="15" t="n"/>
@@ -10966,18 +10971,19 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>• Grafica la curva S del contrato (programado vs ejecutado vs financiero).
-• Muestra el cruce concepto × periodo (mes por mes).
-• Filtra por concepto, periodo o estado de ejecución.
-• Calcula el porcentaje de avance global y por concepto.</t>
+          <t>• Visualiza el programa de obra como matriz concepto × periodo (tipo Gantt), marcando con color los periodos ejecutados vs no ejecutados respecto a lo programado.
+• Muestra el catálogo de conceptos del contrato (lista consultable).
+• Grafica las curvas de avance: programado vs ejecutado vs financiero (curva S).
+• Filtra por concepto, periodo o estado de ejecución; calcula el porcentaje de avance global y por concepto.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>• No registra el avance (eso lo hace SRV-02-02 y la bitácora).
-• No genera alertas (eso lo hace SRV-02-03, y solo si el usuario las configura).
-• No exporta la gráfica a PDF (eso lo hace SRV-06-03).
-• No proyecta cuándo terminará el contrato (es visualización del estado actual, no predicción).</t>
+          <t>• No registra el avance (SRV-02-02 y la bitácora).
+• No edita el catálogo ni el programa (el alta es de SRV-01-01).
+• No genera alertas (SRV-02-03).
+• No exporta a PDF (SRV-06-03).
+• No proyecta la fecha de término (muestra estado actual, no predicción).</t>
         </is>
       </c>
       <c r="G6" s="15" t="n"/>
@@ -11141,18 +11147,20 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>• Genera la bitácora electrónica única para el contrato.
-• Liga al contratista, la supervisión y la residencia con sus datos de contacto.
-• Define quiénes están autorizados a firmar por cada parte.
-• Marca la fecha y hora de apertura como evento formal.
-• Habilita el módulo de bitácora para emitir notas (SRV-03-02).</t>
+          <t>• Apertura la bitácora electrónica única del contrato en la fecha de entrega del sitio de los trabajos, evento que marca el inicio formal y legal de la comunicación vinculante entre las partes (art. 122 RLOPSRM).
+• Liga a las tres partes (dependencia, supervisión, contratista) con sus datos de contacto y sus representantes autorizados a firmar (residente, supervisor externo si existe, superintendente de construcción).
+• Registra la primera nota (nota de apertura) con los datos obligatorios: identificación del contrato, objeto de los trabajos, datos financieros, cronograma contractual y registro de firmas.
+• Captura la firma conjunta de los tres representantes al aperturar.
+• Marca la fecha y hora de apertura como evento formal inalterable.
+• Habilita el módulo de notas (SRV-03-02).</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>• No emite notas (eso lo hace SRV-03-02).
-• No se puede repetir: una vez abierta, no se vuelve a abrir.
-• No cierra la bitácora (el cierre es parte del finiquito, Etapa 2).</t>
+          <t>• No emite notas posteriores a la apertura (SRV-03-02).
+• No se vuelve a aperturar una vez registrada la apertura.
+• No cierra la bitácora (es parte del finiquito, Etapa 2 — fuera de alcance).
+• No registra apertura sin la firma conjunta de los tres autorizados.</t>
         </is>
       </c>
       <c r="G9" s="15" t="n"/>
@@ -11200,20 +11208,22 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>• Permite emitir las notas tipificadas que corresponden al rol del usuario.
-• Asigna folio correlativo automático, fecha y hora del sistema y firmante.
-• Permite vincular respuestas a una nota previa por referencia explícita.
+          <t>• Permite emitir las notas tipificadas que corresponden al rol del usuario, pudiendo incorporar también otro tipo de nota para registrar eventos no tipificados.
+• Asigna folio correlativo automático (sin saltos, manejando concurrencia de los tres usuarios), fecha y hora del sistema y firmante.
 • Acepta los eventos formales del contrato: causas de atraso, instrucciones técnicas, entregas de obra, acuerdos entre partes, solicitudes de información y respuestas.
+• Permite vincular respuestas o correcciones a una nota previa por referencia explícita (formato «dice / debe decir» para correcciones).
+• Captura la firma conjunta de los tres participantes (residente, supervisión y contratista) en cada nota emitida — comportamiento de libro de actas.
 • Permite adjuntar archivos como soporte (fotografías, planos, oficios) hasta 10 MB por archivo.
-• Garantiza inmutabilidad: las notas firmadas no se pueden modificar ni eliminar.</t>
+• Garantiza inmutabilidad: una vez firmada, la nota no se puede modificar ni eliminar (correcciones = nota vinculada nueva).
+• Fundamento: arts. 122 y 125 RLOPSRM.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
           <t>• No permite borrar notas (las correcciones se hacen con notas nuevas vinculadas).
-• No permite a un rol emitir notas que no le corresponden (residente no puede emitir nota de contratista).
+• No permite a un rol emitir notas tipificadas que no le corresponden (residente no puede emitir una nota propia del contratista).
 • No valida el contenido técnico de la nota (la responsabilidad sigue siendo de quien firma).
-• No envía las notas a entidades externas (es bitácora interna del contrato).</t>
+• No envía las notas a entidades externas (bitácora interna del contrato).</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -11267,17 +11277,18 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>• Buscador con filtros: tipo, fecha, firmante, estatus, tema.
+          <t>• Buscador de notas de la bitácora con los siguientes filtros combinables con lógica Y (AND): tipo de nota, rango de fechas (desde / hasta), firmante (quién escribió la nota), vínculo (notas vinculadas a otra previa / sin vínculo), palabra clave sobre el contenido (búsqueda simple por coincidencia de texto, mediante PostgreSQL ILIKE).
 • Filtra por rol del emisor o destinatario.
-• Permite seleccionar varias notas para adjuntar a una estimación.
-• Exportación básica del listado (PDF/Excel).</t>
+• Permite seleccionar varias notas del resultado y exportarlas a formato Excel.
+• Devuelve solo las notas que cumplen simultáneamente todos los filtros aplicados.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
           <t>• No edita las notas encontradas.
 • No re-firma las notas (la firma sigue siendo la original).
-• No hace búsqueda semántica avanzada (es búsqueda por metadatos, no por contenido completo).</t>
+• No hace búsqueda semántica (es coincidencia simple de texto, no análisis semántico).
+• No adjunta notas a una estimación (esa función se realiza desde el armado de la estimación, SRV-04-01).</t>
         </is>
       </c>
       <c r="G11" s="15" t="n"/>
@@ -11385,16 +11396,16 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>• Abre el periodo de estimación N dentro del plazo legal (art. 54 LOPSRM).
-• Permite armar carátula, números generadores, registro fotográfico y soportes.
-• Liga las notas de bitácora del periodo a la estimación.
+          <t>• Abre el periodo de estimación N dentro del plazo legal de presentación (art. 54 LOPSRM).
+• Permite armar la carátula, los números generadores, el registro fotográfico y los soportes de la estimación.
+• Permite buscar y seleccionar notas de bitácora del periodo (usando SRV-03-03) para vincularlas a la estimación.
 • Guarda toda la estimación como una sola entidad cohesionada.
-• Calcula automáticamente totales por concepto y periodo.</t>
+• Calcula automáticamente los totales por concepto y periodo, y las cantidades de la carátula: anticipo amortizado, retenciones legales (5 al millar, art. 191 LFD) y deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>• No envía la estimación a revisión (eso es SRV-04-02).
+          <t>• No envía la estimación a revisión (SRV-04-02).
 • No valida internamente contra catálogo o programa (eso lo hace la supervisión en SRV-05-01).
 • No carga conceptos que no estén en el catálogo del contrato.
 • No permite mezclar periodos (una estimación es de un solo periodo).</t>
@@ -11971,17 +11982,19 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>• Permite a Finanzas capturar el pago efectuado.
-• Registra fecha, importe, referencia bancaria y observaciones.
+          <t>• Permite a Finanzas registrar el pago ya realizado de una estimación autorizada.
+• Captura los datos obligatorios: fecha, importe, referencia bancaria, observaciones y usuario que realizó el registro.
+• Valida que todos los datos obligatorios estén completos antes de permitir guardar el registro.
 • Actualiza el avance financiero del contrato.
-• Cierra el ciclo de la estimación pagada.</t>
+• Marca la estimación como pagada y cierra el ciclo de esa estimación.</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>• No transfiere el dinero (esa transferencia es operación bancaria fuera del sistema).
-• No emite el comprobante de pago.
-• No registra pagos parciales (el pago se asume completo según lo autorizado).</t>
+          <t>• No transfiere el dinero (esa operación es bancaria, fuera del sistema).
+• No emite el comprobante de pago (lo emite el banco).
+• No registra pagos parciales (el pago se asume completo según lo autorizado).
+• No genera la instrucción de pago (eso lo hace SRV-07-01, HU-20).</t>
         </is>
       </c>
       <c r="G22" s="15" t="n"/>

--- a/docs/matriz_DEFINITIVA.xlsx
+++ b/docs/matriz_DEFINITIVA.xlsx
@@ -378,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -560,6 +560,24 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10624,7 +10642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" style="48" min="1" max="1"/>
@@ -10697,27 +10715,88 @@
       </c>
     </row>
     <row r="2" ht="102" customHeight="1" s="48">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
+        <is>
+          <t>SRV-00-01</t>
+        </is>
+      </c>
+      <c r="B2" s="72" t="inlineStr">
+        <is>
+          <t>MOD-00</t>
+        </is>
+      </c>
+      <c r="C2" s="72" t="inlineStr">
+        <is>
+          <t>Control de Accesos (transversal)</t>
+        </is>
+      </c>
+      <c r="D2" s="72" t="inlineStr">
+        <is>
+          <t>Cuando cualquier usuario entra al sistema se autentica y el sistema deduce su rol; toda operación posterior verifica autenticación y permisos antes de ejecutar.</t>
+        </is>
+      </c>
+      <c r="E2" s="73" t="inlineStr">
+        <is>
+          <t>• Autentica usuarios contra el repositorio del sistema (correo + contraseña, hash bcrypt).
+• Emite token de sesión (JWT, 8 h de vigencia) tras autenticación exitosa.
+• Deduce el rol del usuario a partir de su identificador, sin selección explícita.
+• Filtra las pantallas y opciones según el rol (residente, contratista, supervisión, dependencia, finanzas).
+• Registra cada acción del usuario con su nombre y fecha/hora para auditoría.
+• Es servicio transversal: todos los demás servicios verifican autenticación y rol antes de ejecutar.</t>
+        </is>
+      </c>
+      <c r="F2" s="74" t="inlineStr">
+        <is>
+          <t>• No gestiona altas de usuarios (administración fuera del sistema).
+• No recupera contraseñas olvidadas (proceso administrativo aparte).
+• No expone la contraseña en ningún momento (siempre hash bcrypt).
+• No permite ninguna operación sin autenticación válida.</t>
+        </is>
+      </c>
+      <c r="G2" s="75" t="inlineStr"/>
+      <c r="H2" s="76" t="inlineStr">
+        <is>
+          <t>Muy alta</t>
+        </is>
+      </c>
+      <c r="I2" s="77" t="inlineStr">
+        <is>
+          <t>Etapa 1</t>
+        </is>
+      </c>
+      <c r="J2" s="72" t="inlineStr">
+        <is>
+          <t>Transversal a todos los servicios</t>
+        </is>
+      </c>
+      <c r="K2" s="72" t="inlineStr">
+        <is>
+          <t>Todos los roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="102" customHeight="1" s="48">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>SRV-01-01</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>MOD-01</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Alta y configuración del contrato</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Cuando llega un contrato nuevo, la dependencia lo carga al sistema en un solo flujo: los datos generales (folio, partes, monto, fechas, modalidad de pago), el catálogo de conceptos con sus precios unitarios, el programa de obra con su calendario y los elementos jurídicos del contratista (representante legal, capital social, registros). Todo queda guardado junto como la 'configuración inicial' del contrato, y desde ahí los demás módulos del sistema lo consultan.</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>• Captura los datos generales del contrato (folio único, partes, monto, plazos, modalidad de pago).
 • Carga el catálogo de conceptos completo (clave, descripción, unidad, precio unitario, cantidad contratada).
@@ -10730,7 +10809,7 @@
 • Versiona la configuración inicial para que pueda actualizarse por modificatorios (SRV-01-03).</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>• No genera el contrato (ya está firmado fuera del sistema antes de capturarse).
 • No edita el PDF firmado (es inmutable; cualquier cambio requiere modificatorio).
@@ -10740,113 +10819,114 @@
 • No registra estimaciones ni pagos (SRV-04-* / SRV-07-*).</t>
         </is>
       </c>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>DEP-01; DEP-02; RES-09; CON-05; SUP-01</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Dependencia; Residente; Contratista/Superintendente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="102" customHeight="1" s="48">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="4" ht="114.75" customHeight="1" s="48">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>SRV-01-02</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>MOD-01</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Registro de fianzas y garantías</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>El contratista entrega pólizas de fianza (cumplimiento, vicios ocultos, anticipo) y la dependencia las sube al sistema. Más allá del documento, el sistema captura sus metadatos: vigencia, fecha de inicio, fecha de vencimiento, afianzadora y monto afianzado. Cuando una fianza está por vencer, el sistema avisa con anticipación para que las partes actúen a tiempo.</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>• Permite subir el PDF de cada póliza (cumplimiento, vicios ocultos, anticipo).
 • Captura los metadatos clave: vigencia, afianzadora, monto.
-• Manda alerta cuando una póliza está por vencer (configurable: N días antes).
-• Mantiene historial de todas las fianzas del contrato.</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>• No emite ni valida pólizas (las pólizas las emite la afianzadora).
+• Emite alertas cuando una póliza está por vencer en plazos 30, 15 y 5 días antes del vencimiento (configurables).
+• Mantiene el historial de todas las fianzas del contrato, incluyendo endosos por modificatorios.
+• Fundamento: art. 48 LOPSRM.</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>• No emite ni valida pólizas (las emite la afianzadora).
 • No verifica que la afianzadora esté autorizada por la CNSF.
-• No tramita los endosos por modificatorio (eso lo hace SRV-01-03).
-• No ejecuta fianzas en caso de incumplimiento (ese es un proceso administrativo aparte).</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
+• No tramita endosos por modificatorio (lo hace SRV-01-03).
+• No ejecuta fianzas en incumplimiento.</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Alerta por proximidad de vencimiento de póliza (configurable: N días antes del vencimiento). Las pólizas de cumplimiento y anticipo se otorgan conforme al art. 48 LOPSRM (cumplimiento del contrato y garantía de anticipo).</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>DEP-09; FIN-06; FIN-07</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Dependencia; Finanzas; Residente</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="114.75" customHeight="1" s="48">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="5" ht="76.5" customHeight="1" s="48">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>SRV-01-03</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>MOD-01</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Trámite y aplicación de convenios modificatorios</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Cuando hace falta cambiar algo del contrato (monto, plazo, conceptos), el sistema acompaña todo el proceso del convenio modificatorio: desde que el contratista lo solicita, pasando por el análisis técnico y la autorización, hasta que se aplican las actualizaciones al catálogo, al programa y a las fianzas. Queda guardado el histórico completo, así que en cualquier momento se puede ver qué cambió, cuándo y por qué.</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>• Registra la solicitud del modificatorio con su justificación.
 • Guarda los oficios de análisis y autorización.
@@ -10856,7 +10936,7 @@
 • Mantiene el histórico de versiones con fecha, autor y motivo.</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>• No autoriza el modificatorio (eso es una decisión humana de la dependencia, art. 59 LOPSRM).
 • No calcula la suficiencia presupuestal (esa revisión es parte del proceso administrativo previo).
@@ -10864,112 +10944,112 @@
 • No edita versiones anteriores (siempre se crea una nueva versión, las anteriores quedan intactas).</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Histórico inmutable de versiones del catálogo y programa con fecha, autor y motivo del cambio (art. 59 LOPSRM).</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>RES-11; CON-11; CON-12; CON-19</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Residente; Contratista/Superintendente; Dependencia; Supervisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="76.5" customHeight="1" s="48">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>SRV-01-04</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>MOD-01</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Consulta integrada del expediente contractual</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Es la pantalla para cuando alguien necesita 'ver todo' de un contrato sin meterse a editar nada. Ahí está la configuración vigente, el catálogo, el programa actualizado, las fianzas y los elementos jurídicos en un solo lugar, con buscador para encontrar rápido lo que se necesita.</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>• Muestra en una sola vista todo el expediente del contrato.
-• Permite buscar por folio, contratista, objeto, periodo o estado.
-• Descarga documentos individuales del expediente.
-• Filtra por tipo de documento.</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>• No permite editar ningún campo (es solo lectura).
-• No descarga el expediente completo en un solo archivo comprimido (eso lo hace SRV-06-03).
-• No muestra datos de otros contratos del mismo contratista (eso lo hace SRV-06-02).</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Etapa 1</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>RES-16; SUP-01</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>Residente; Supervisión; Dependencia</t>
         </is>
       </c>
     </row>
     <row r="6" ht="89.25" customHeight="1" s="48">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>SRV-01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>MOD-01</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Consulta integrada del expediente contractual</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Es la pantalla para cuando alguien necesita 'ver todo' de un contrato sin meterse a editar nada. Ahí está la configuración vigente, el catálogo, el programa actualizado, las fianzas y los elementos jurídicos en un solo lugar, con buscador para encontrar rápido lo que se necesita.</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>• Muestra en una sola vista los 5 bloques del expediente: configuración (datos generales), catálogo, programa, fianzas y documentos jurídicos.
+• Permite buscar y filtrar por folio, contratista, objeto, periodo o tipo de documento, aplicando los filtros con lógica Y (AND) sobre los bloques.
+• Permite descargar documentos individuales del expediente (PDF de contrato, pólizas, oficios, etc.).
+• Es vista de solo lectura (la edición se hace en HU-01 o vía modificatorio HU-03).</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>• No permite editar ningún campo (es solo lectura).
+• No descarga el expediente completo en un solo archivo comprimido (SRV-06-03).
+• No muestra datos de otros contratos del mismo contratista (SRV-06-02).</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Etapa 1</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>RES-16; SUP-01</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Residente; Supervisión; Dependencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="102" customHeight="1" s="48">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
           <t>SRV-02-01</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>MOD-02</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Visualización del programa y curva de avance</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Muestra cómo va el contrato físicamente y financieramente: lo que estaba programado para cada mes, lo que realmente se ejecutó, y lo que ya se cobró. La curva S que la dependencia y la residencia usan para saber si el contrato va bien, adelantado o atrasado.</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>• Visualiza el programa de obra como matriz concepto × periodo (tipo Gantt), marcando con color los periodos ejecutados vs no ejecutados respecto a lo programado.
 • Muestra el catálogo de conceptos del contrato (lista consultable).
@@ -10977,7 +11057,7 @@
 • Filtra por concepto, periodo o estado de ejecución; calcula el porcentaje de avance global y por concepto.</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>• No registra el avance (SRV-02-02 y la bitácora).
 • No edita el catálogo ni el programa (el alta es de SRV-01-01).
@@ -10986,50 +11066,50 @@
 • No proyecta la fecha de término (muestra estado actual, no predicción).</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>RES-09; SUP-02; RES-18; DEP-12</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Residente; Supervisión; Contratista/Superintendente; Dependencia</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="102" customHeight="1" s="48">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="8" ht="76.5" customHeight="1" s="48">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>SRV-02-02</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>MOD-02</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Registro de trabajos terminados por concepto y periodo</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Cada vez que el contratista termina trabajos en un periodo, los registra aquí: cuánto hizo de cada concepto. Este registro es la base para armar la estimación después, y se conecta con las notas de bitácora del tipo Entrega para que cada cantidad reportada tenga su respaldo documental.</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>• Permite al contratista capturar las cantidades ejecutadas por concepto y periodo.
 • Vincula cada registro con su nota de bitácora correspondiente.
@@ -11037,57 +11117,57 @@
 • Detecta cuando una cantidad reportada excede lo contratado.</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>• No autoriza ni valida lo reportado (eso lo hace la supervisión en la estimación).
 • No calcula montos a cobrar (eso es parte de la estimación, SRV-04-01).
 • No reemplaza la verificación física en obra (es solo el registro).</t>
         </is>
       </c>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>CON-05</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Contratista/Superintendente; Residente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="76.5" customHeight="1" s="48">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="9" ht="102" customHeight="1" s="48">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>SRV-02-03</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>MOD-02</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Configuración de alertas de atraso por concepto</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Es una herramienta a disposición del residente y de la supervisión para que cada quien configure qué quiere vigilar y cuándo quiere que le avisen. Si nadie configura nada, el sistema no manda alertas; así se evita el ruido de notificaciones que no aportan.</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>• Permite al usuario elegir qué conceptos quiere vigilar.
 • Define el umbral de atraso a partir del cual se quiere ser notificado.
@@ -11095,57 +11175,57 @@
 • Permite pausar o desactivar las alertas configuradas.</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>• No genera alertas por sí solo (todo se configura primero).
 • No determina las causas del atraso (eso lo hace la bitácora con sus notas).
 • No genera consecuencias contractuales por atraso (eso es decisión humana).</t>
         </is>
       </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>RES-10; SUP-08</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Residente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="102" customHeight="1" s="48">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="178.5" customHeight="1" s="48">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>SRV-03-01</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>MOD-03</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Apertura formal de la bitácora del contrato</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Es el acto formal con el que arranca la bitácora electrónica de un contrato: se ligan las tres partes (contratante a través de la residencia, supervisión y contratista a través del superintendente), se definen los responsables autorizados a firmar por cada rol, y queda habilitada para registrar los eventos formales del contrato mediante notas tipificadas. Es un paso único por contrato, conforme al art. 46 último párrafo LOPSRM y al art. 122 RLOPSRM.</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>• Apertura la bitácora electrónica única del contrato en la fecha de entrega del sitio de los trabajos, evento que marca el inicio formal y legal de la comunicación vinculante entre las partes (art. 122 RLOPSRM).
 • Liga a las tres partes (dependencia, supervisión, contratista) con sus datos de contacto y sus representantes autorizados a firmar (residente, supervisor externo si existe, superintendente de construcción).
@@ -11155,7 +11235,7 @@
 • Habilita el módulo de notas (SRV-03-02).</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>• No emite notas posteriores a la apertura (SRV-03-02).
 • No se vuelve a aperturar una vez registrada la apertura.
@@ -11163,50 +11243,50 @@
 • No registra apertura sin la firma conjunta de los tres autorizados.</t>
         </is>
       </c>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>RES-01</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Residente; Contratista/Superintendente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="178.5" customHeight="1" s="48">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11" ht="76.5" customHeight="1" s="48">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>SRV-03-02</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>MOD-03</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Emisión y respuesta de notas tipificadas con firma</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Es el corazón de la bitácora. Cada persona autorizada (residente, supervisión, contratista) puede emitir las notas que le corresponden conforme al art. 125 RLOPSRM (instrucción, acuerdo, solicitud, confirmación, respuesta), y responder cualquier nota dirigida a ella. Una vez firmadas, las notas no se editan ni se borran: si hay un error o algo cambia, se emite una nueva nota vinculada. Así queda el historial completo y defendible, conforme al art. 46 último párrafo LOPSRM y a los arts. 123 y 125 RLOPSRM.</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>• Permite emitir las notas tipificadas que corresponden al rol del usuario, pudiendo incorporar también otro tipo de nota para registrar eventos no tipificados.
 • Asigna folio correlativo automático (sin saltos, manejando concurrencia de los tres usuarios), fecha y hora del sistema y firmante.
@@ -11218,7 +11298,7 @@
 • Fundamento: arts. 122 y 125 RLOPSRM.</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>• No permite borrar notas (las correcciones se hacen con notas nuevas vinculadas).
 • No permite a un rol emitir notas tipificadas que no le corresponden (residente no puede emitir una nota propia del contratista).
@@ -11226,56 +11306,56 @@
 • No envía las notas a entidades externas (bitácora interna del contrato).</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>1) Inmutabilidad: notas firmadas no se editan ni borran; correcciones por nota adicional vinculada (art. 123 RLOPSRM).
 2) Plazo de firma configurable por contrato. Vencido el plazo, la nota se considera notificada; esto NO implica aceptación del contenido.
 3) Cada rol solo puede emitir los tipos de nota que le corresponden conforme al art. 125 RLOPSRM.</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>CON-01; RES-02; CON-02; RES-03; CON-04</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Residente; Contratista/Superintendente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="76.5" customHeight="1" s="48">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="12" ht="114.75" customHeight="1" s="48">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>SRV-03-03</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>MOD-03</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Consulta y búsqueda de notas</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Cuando alguien necesita encontrar una nota específica de bitácora (porque la quiere referenciar en una estimación, en una minuta o en un oficio), aquí puede buscarla por tipo, fecha, firmante, estatus o tema. Es la herramienta que conecta la bitácora con el resto del sistema.</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>• Buscador de notas de la bitácora con los siguientes filtros combinables con lógica Y (AND): tipo de nota, rango de fechas (desde / hasta), firmante (quién escribió la nota), vínculo (notas vinculadas a otra previa / sin vínculo), palabra clave sobre el contenido (búsqueda simple por coincidencia de texto, mediante PostgreSQL ILIKE).
 • Filtra por rol del emisor o destinatario.
@@ -11283,7 +11363,7 @@
 • Devuelve solo las notas que cumplen simultáneamente todos los filtros aplicados.</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>• No edita las notas encontradas.
 • No re-firma las notas (la firma sigue siendo la original).
@@ -11291,50 +11371,50 @@
 • No adjunta notas a una estimación (esa función se realiza desde el armado de la estimación, SRV-04-01).</t>
         </is>
       </c>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>RES-04; CON-03; SUP-03</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Residente; Contratista/Superintendente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="114.75" customHeight="1" s="48">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="13" ht="114.75" customHeight="1" s="48">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>SRV-03-04</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>MOD-03</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Registro y agenda de minutas, visitas e inspecciones</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Permite registrar las minutas de las reuniones de seguimiento (subiendo el documento con sus metadatos: fecha, asistentes, tema, acuerdos) y administrar la agenda de visitas e inspecciones del contrato. Las visitas se planean por fecha, lugar y responsable, y al hacerse se vinculan a la minuta o nota de bitácora correspondiente. El sistema concentra todas las reuniones, los acuerdos asentados, los compromisos derivados y las visitas en un solo lugar para consulta por las partes.</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>• Permite subir el PDF de la minuta con sus metadatos.
 • Permite agendar visitas e inspecciones con fecha, lugar, responsable y propósito.
@@ -11343,7 +11423,7 @@
 • Permite adjuntar una minuta o registro de visita como referencia en una nota de bitácora.</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>• No redacta minutas (las redacta quien convoca la reunión).
 • No da seguimiento automático a los acuerdos asentados.
@@ -11351,50 +11431,50 @@
 • No transcribe audios ni hace minutas a partir de grabaciones.</t>
         </is>
       </c>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>RES-14; SUP-07; SUP-11; SUP-15; CON-16</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Residente; Supervisión; Contratista/Superintendente</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="114.75" customHeight="1" s="48">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="14" ht="127.5" customHeight="1" s="48">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>SRV-04-01</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>MOD-04</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Apertura del periodo e integración de la estimación</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Cuando el contratista quiere cobrar lo que hizo en un periodo, abre la estimación y la arma como un expediente completo: carátula, números generadores, registro fotográfico, croquis, soportes y notas de bitácora que respaldan el avance. Todo en un solo flujo, todo en un solo bloque. La apertura del periodo controla el plazo de presentación: el sistema solo permite abrirla y enviarla dentro de los 6 días naturales tras el corte del periodo, conforme al art. 54 LOPSRM.</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>• Abre el periodo de estimación N dentro del plazo legal de presentación (art. 54 LOPSRM).
 • Permite armar la carátula, los números generadores, el registro fotográfico y los soportes de la estimación.
@@ -11403,7 +11483,7 @@
 • Calcula automáticamente los totales por concepto y periodo, y las cantidades de la carátula: anticipo amortizado, retenciones legales (5 al millar, art. 191 LFD) y deductivas por penalizaciones según el contrato.</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>• No envía la estimación a revisión (SRV-04-02).
 • No valida internamente contra catálogo o programa (eso lo hace la supervisión en SRV-05-01).
@@ -11411,55 +11491,55 @@
 • No permite mezclar periodos (una estimación es de un solo periodo).</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>1) Apertura del periodo conforme al plazo del contrato y al art. 132 RLOPSRM (documentos soporte que acompañan la estimación).
 2) Cálculos administrativos en la carátula: anticipo y su amortización (art. 50 LOPSRM), retenciones legales (5 al millar conforme al art. 191 LFD) y deductivas por penalizaciones (art. 46 Bis LOPSRM).</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>CON-07; CON-06; CON-08; SUP-12</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Contratista/Superintendente; Residente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="127.5" customHeight="1" s="48">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="15" ht="114.75" customHeight="1" s="48">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>SRV-04-02</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>MOD-04</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Envío de la estimación</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Cuando el contratista termina de integrar la estimación, la envía formalmente para revisión. El botón de enviar solo está habilitado si la presentación está dentro de los 6 días naturales tras el corte del periodo (art. 54 LOPSRM). Al enviarla, el sistema marca la fecha de recepción, arranca el plazo de revisión y notifica a la supervisión y a la residencia. La única pre-validación es que las cantidades no excedan el catálogo vigente; cualquier otra revisión técnica corresponde a la supervisión en su revisión formal.</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>• Habilita el botón 'Enviar' solo dentro del plazo legal de 6 días.
 • Verifica que las cantidades no excedan lo contratado en el catálogo vigente.
@@ -11468,7 +11548,7 @@
 • Inicia el plazo de revisión (15 días supervisión + 5 días autorización residencia).</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>• No hace pre-validación técnica de la estimación (eso es responsabilidad del contratista).
 • No verifica que los números cuadren contra el programa (eso lo hace la supervisión en SRV-05-01).
@@ -11476,55 +11556,55 @@
 • No permite enviar fuera del plazo legal de 6 días (botón deshabilitado).</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>1) Plazo de envío: 6 días naturales tras corte del periodo (art. 54 LOPSRM). Vencido el plazo, el botón 'Enviar' queda deshabilitado.
 2) Validación de cantidades contra catálogo: si una cantidad excede lo contratado, el sistema regresa la estimación al contratista sin enviarla.</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>CON-06; RES-05; CON-07; CON-14</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Contratista/Superintendente; Residente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="114.75" customHeight="1" s="48">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="16" ht="191.25" customHeight="1" s="48">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>SRV-04-03</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>MOD-04</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Historial de estimaciones del contrato</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Una vista de consulta cronológica de todas las estimaciones del contrato. Permite filtrar por estado para ver las aceptadas, las rechazadas o las que están en proceso. Importante: solo puede haber UNA estimación aceptada por periodo, pero puede haber múltiples rechazadas (cada reingreso queda como una versión nueva en el historial).</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>• Lista todas las estimaciones del contrato en orden cronológico.
 • Permite filtrar por estado: aceptadas, rechazadas, en proceso.
@@ -11533,61 +11613,61 @@
 • Muestra cuántas veces se presentó cada periodo (versiones rechazadas + aceptada final).</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>• No edita estimaciones (es vista de consulta).
 • No genera nuevas estimaciones (eso es SRV-04-01).
 • No compara versiones entre sí (es solo listado por estado).</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>Solo puede haber UNA estimación aceptada por periodo; las rechazadas previas quedan en el historial.</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>RES-08; CON-09</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Residente; Contratista/Superintendente; Dependencia</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="191.25" customHeight="1" s="48">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17" ht="89.25" customHeight="1" s="48">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>SRV-05-01</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>MOD-05</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Recepción, revisión, observaciones y autorización/rechazo de la estimación</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Al recibirse la estimación, el sistema notifica a residencia, supervisión y superintendente que la revisión está en proceso. Muestra la estimación completa en una sola pantalla, organizada por sección (carátula, números generadores, registro fotográfico, soportes y notas de bitácora ligadas). Permite a la supervisión hacer la revisión técnica con pre-validación de números y observaciones puntuales por sección y por concepto, con la opción de rechazar o pasar el turno a residencia mediante el flujo de turnado. La residencia toma la decisión final de autorización o rechazo. Al autorizar, el sistema registra en la carátula los conceptos administrativos correspondientes (anticipo y su amortización, retenciones legales como el 5 al millar, deductivas por penalizaciones) y calcula el importe neto a pagar.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>• Notifica formalmente a residencia, supervisión y superintendente al recibir la estimación.
 • Muestra la estimación completa por sección: carátula, números generadores, registro fotográfico, soportes, notas de bitácora.
@@ -11599,7 +11679,7 @@
 • Manda alertas si se acercan los plazos del art. 54 LOPSRM.</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>• No verifica físicamente en obra (esa es supervisión de campo aparte).
 • No paga la estimación (eso lo hace SRV-07-02 de Finanzas).
@@ -11607,56 +11687,56 @@
 • No permite editar la estimación durante la revisión (el contratista debe reingresarla).</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>1) Plazo de revisión y autorización: hasta 15 días naturales tras la presentación de la estimación (art. 54 LOPSRM). El pago corre por separado (ver SRV-07-01).
 2) Afirmativa ficta del art. 133 RLOPSRM: si no se emiten observaciones en el plazo, se considera que no las hay.
 3) Anticipos y amortización conforme art. 50 LOPSRM; retenciones y deductivas según contrato.</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>RES-05; RES-06; RES-07; SUP-05; SUP-06; DEP-13; SUP-09; DEP-03; DEP-04</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Residente; Supervisión; Dependencia</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="89.25" customHeight="1" s="48">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="18" ht="102" customHeight="1" s="48">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>SRV-05-02</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>MOD-05</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Reingreso de estimación tras rechazo</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Si una estimación es rechazada, el contratista debe presentar una nueva versión completa de la estimación atendiendo los puntos observados. El nuevo envío se trata como un bloque completamente nuevo (no como edición parcial de la rechazada); la revisión empieza de cero sobre la nueva versión. La versión rechazada queda en el historial para trazabilidad.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>• Permite descargar el listado de observaciones en PDF o Excel.
 • Genera una nueva versión completa de la estimación del mismo periodo.
@@ -11664,7 +11744,7 @@
 • Vincula la nueva versión con la rechazada para trazabilidad.</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>• No edita la versión rechazada (queda como histórico inmutable).
 • No hace seguimiento puntual de qué observaciones se atendieron (es un bloque nuevo completo).
@@ -11672,50 +11752,50 @@
 • No notifica automáticamente a la supervisión (lo hace el contratista al enviarla).</t>
         </is>
       </c>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>CON-10</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Contratista/Superintendente; Residente</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="102" customHeight="1" s="48">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19" ht="165.75" customHeight="1" s="48">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>SRV-06-01</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>MOD-06</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Tablero de seguimiento de estimaciones aceptadas y en revisión</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Una pantalla donde los actores autorizados del contrato (residente, supervisión, contratista, dependencia) ven la línea de tiempo de las estimaciones aceptadas y de las que están en proceso: presentada, en revisión, autorizada, en pago, pagada. NO se muestran rechazadas (las rechazadas viven en el historial, SRV-04-03). El tablero también concentra los pendientes por solventar por cada actor: observaciones abiertas, documentos faltantes, notas sin firmar dentro del plazo configurado.</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>• Lista las estimaciones aceptadas y en revisión con su estado actual.
 • Muestra línea de tiempo por estimación: presentada → revisada → autorizada → en pago → pagada.
@@ -11724,7 +11804,7 @@
 • Permite filtrar por estado, por periodo o por responsable.</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>• No muestra estimaciones rechazadas (esas viven en SRV-04-03).
 • No edita estimaciones (es solo seguimiento).
@@ -11732,56 +11812,56 @@
 • No envía recordatorios automáticos (los configura cada usuario en SRV-02-03).</t>
         </is>
       </c>
-      <c r="G18" s="68" t="inlineStr">
+      <c r="G19" s="68" t="inlineStr">
         <is>
           <t>1) El tablero excluye estimaciones rechazadas; estas viven en el historial (SRV-04-03).
 2) Los pendientes por solventar se filtran por rol del usuario autenticado: cada actor ve solo lo que le corresponde resolver.
 3) La línea de tiempo muestra los estados en orden: presentada → en revisión → autorizada → en pago → pagada.</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>CON-09; RES-08; RES-13; CON-17; SUP-14</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>Residente; Contratista/Superintendente; Supervisión; Dependencia</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="165.75" customHeight="1" s="48">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20" ht="409.5" customHeight="1" s="48">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>SRV-06-02</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>MOD-06</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Vista ejecutiva con semáforos y drill-down al contrato</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Es la pantalla ejecutiva para la dependencia: muestra los contratos asignados al usuario logueado como una lista con un semáforo de uno de tres colores (verde, ámbar o rojo) por contrato, calculado a partir de su avance físico contra programado, atrasos en plazos y pendientes sin atender. Al hacer doble clic sobre un contrato, se hace drill-down al detalle del contrato: indicadores físicos y financieros, penalizaciones aplicadas y agrupaciones por contratista o por ejercicio fiscal.</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>• Lista los contratos asignados al usuario logueado con su semáforo de color.
 • Calcula el color del semáforo según tres factores: avance físico vs programado, atrasos en plazos legales y pendientes sin atender.
@@ -11791,7 +11871,7 @@
 • Compara periodos (mes actual vs mes anterior).</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>• No edita datos (consulta agregada únicamente).
 • No reemplaza al tablero operativo del contrato (SRV-06-01).
@@ -11799,50 +11879,50 @@
 • No proyecta escenarios futuros (es vista del estado actual).</t>
         </is>
       </c>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>DEP-05; SUP-10; DEP-11; DEP-14; RES-17</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Dependencia; Residente; Supervisión</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="409.5" customHeight="1" s="48">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21" ht="178.5" customHeight="1" s="48">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>SRV-06-03</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>MOD-06</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Exportación de reportes definidos del contrato</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Permite descargar siete reportes específicos del contrato en formatos definidos, para llevar información del sistema hacia procesos externos (oficios, presentaciones, expedientes auditables). Los reportes están predefinidos: el usuario no construye reportes ad-hoc, solo selecciona uno de los siete y el periodo (mensual, trimestral, acumulado del contrato). Cada reporte tiene su formato fijo (PDF, Excel, o ambos) y su contenido fijo, descritos en la columna 'Qué hace'.</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Los SIETE reportes definidos son:
 1. Avance físico vs programado (PDF gráfico + Excel tabular): curva S del contrato y tabla concepto × periodo con cantidades programadas, ejecutadas y porcentaje de avance.
@@ -11854,7 +11934,7 @@
 7. Penalizaciones y deductivas aplicadas (Excel tabular): una fila por penalización con estimación origen, concepto, monto deducido, fundamento contractual y fecha.</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>• No genera reportes personalizados ad-hoc (solo los siete definidos).
 • No envía reportes por correo automáticamente.
@@ -11863,56 +11943,56 @@
 • No combina reportes en uno solo (cada reporte es un archivo separado).</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>1) Los siete reportes están predefinidos: contenido, formato y estructura son fijos.
 2) El usuario solo puede elegir el periodo (mensual, trimestral o acumulado del contrato).
 3) Cada reporte incluye encabezado con folio del contrato, contratista, periodo cubierto y fecha de generación.</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>RES-15; SUP-13; FIN-13; FIN-15; CON-18</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>Residente; Supervisión; Dependencia; Finanzas; Contratista/Superintendente</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="178.5" customHeight="1" s="48">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="22" ht="63.75" customHeight="1" s="48">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>SRV-07-01</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>MOD-07</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Tránsito a pago y carga de soportes documentales</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Cuando una estimación se autoriza, el sistema verifica primero la suficiencia presupuestal del contrato (compromisos no rebasan el techo del oficio presupuestal anual conforme al art. 24 LOPSRM). Si hay suficiencia, genera la instrucción de pago para Finanzas; si no, se rechaza hasta que exista una ampliación presupuestal autorizada. El contratista sube los soportes definidos por contrato (factura electrónica del periodo, CFDI correspondiente y, si el contrato lo requiere, estado de cuenta vigente de la fianza). Finanzas recibe la notificación y arranca el plazo de 20 días naturales del art. 54 LOPSRM. El sistema lleva el semáforo del plazo y avisa cuando se acerca el vencimiento.</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>• Verifica suficiencia presupuestal del contrato antes de generar la instrucción.
 • Genera la instrucción de pago al autorizarse la estimación.
@@ -11922,7 +12002,7 @@
 • Marca como faltante cualquier soporte definido que no haya sido cargado.</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>• No valida CFDI con el SAT (no se conecta al SAT).
 • No hace cálculos fiscales (eso lo hace el ERP de la dependencia).
@@ -11931,56 +12011,56 @@
 • No autoriza ampliaciones presupuestales (es proceso administrativo aparte).</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>1) Plazo de pago: 20 días naturales desde la autorización (art. 54 LOPSRM); semáforo de vencimientos y alertas a Finanzas y Dependencia.
 2) Suficiencia presupuestal: la estimación no puede rebasar el techo del oficio presupuestal anual (art. 24 LOPSRM); conceptos adicionales requieren ampliación presupuestal previa.
 3) Soportes esperados: factura electrónica del periodo + CFDI correspondiente + estado de cuenta de la fianza de cumplimiento cuando el contrato lo exija en su cláusula de pagos. Si falta alguno, el sistema lo marca como pendiente y notifica al contratista.</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>CON-13; FIN-01; DEP-08; FIN-02; FIN-08; FIN-03; FIN-16; FIN-12; DEP-06; DEP-07; FIN-09</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Residente; Finanzas; Contratista/Superintendente; Dependencia</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="63.75" customHeight="1" s="48">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>SRV-07-02</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>MOD-07</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Registro del pago efectuado</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Cuando Finanzas hace el pago de una estimación, lo registra aquí: fecha, importe, referencia bancaria. El registro cierra el ciclo de la estimación y se refleja en el avance financiero del contrato.</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>• Permite a Finanzas registrar el pago ya realizado de una estimación autorizada.
 • Captura los datos obligatorios: fecha, importe, referencia bancaria, observaciones y usuario que realizó el registro.
@@ -11989,7 +12069,7 @@
 • Marca la estimación como pagada y cierra el ciclo de esa estimación.</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>• No transfiere el dinero (esa operación es bancaria, fuera del sistema).
 • No emite el comprobante de pago (lo emite el banco).
@@ -11997,23 +12077,23 @@
 • No genera la instrucción de pago (eso lo hace SRV-07-01, HU-20).</t>
         </is>
       </c>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>Etapa 1</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>FIN-04</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>Finanzas; Residente; Dependencia</t>
         </is>
